--- a/ekspor-xlsx/sac/penduduk_provinsi_indonesia.xlsx
+++ b/ekspor-xlsx/sac/penduduk_provinsi_indonesia.xlsx
@@ -434,14 +434,14 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>negara</t>
+          <t>country</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -451,22 +451,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>provinsi</t>
+          <t>province</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tahun</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>penduduk</t>
+          <t>population</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>sumber</t>
+          <t>source</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>BPS proyeksi SP2010 (WebAPI)</t>
+          <t>BPS SP2010 projection (WebAPI)</t>
         </is>
       </c>
     </row>
